--- a/data/trans_camb/P2A_enfcro_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,19; 46,49</t>
+          <t>12,58; 47,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 34,25</t>
+          <t>1,32; 32,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,07; 76,0</t>
+          <t>53,31; 75,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 37,72</t>
+          <t>3,24; 37,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 39,43</t>
+          <t>6,58; 37,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,06; 76,68</t>
+          <t>54,89; 76,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,11; 37,81</t>
+          <t>12,79; 37,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,96; 32,13</t>
+          <t>8,65; 32,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,62; 73,42</t>
+          <t>57,94; 73,03</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,47; 173,03</t>
+          <t>29,49; 189,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 129,01</t>
+          <t>3,36; 130,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126,13; 321,75</t>
+          <t>116,82; 319,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,81; 155,76</t>
+          <t>8,28; 151,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,6; 154,68</t>
+          <t>15,37; 148,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>124,13; 338,67</t>
+          <t>123,2; 330,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,87; 138,55</t>
+          <t>34,33; 138,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,43; 119,91</t>
+          <t>20,69; 112,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>139,89; 283,55</t>
+          <t>141,15; 283,27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 16,13</t>
+          <t>-10,06; 18,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 26,38</t>
+          <t>0,18; 27,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,73; 67,92</t>
+          <t>48,6; 69,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 9,77</t>
+          <t>-18,16; 9,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 9,3</t>
+          <t>-16,33; 10,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,62; 55,34</t>
+          <t>32,71; 55,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 9,8</t>
+          <t>-9,74; 10,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 15,5</t>
+          <t>-4,15; 15,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,32; 59,21</t>
+          <t>44,8; 59,35</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 47,63</t>
+          <t>-22,28; 55,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 79,31</t>
+          <t>1,57; 84,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,51; 216,36</t>
+          <t>96,31; 224,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 24,43</t>
+          <t>-33,58; 24,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 22,8</t>
+          <t>-29,68; 24,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,54; 140,07</t>
+          <t>55,92; 141,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 25,2</t>
+          <t>-20,29; 25,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 39,6</t>
+          <t>-8,5; 39,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,31; 156,95</t>
+          <t>88,95; 159,74</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 25,29</t>
+          <t>-3,64; 26,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 14,59</t>
+          <t>-13,85; 14,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,43; 67,96</t>
+          <t>45,21; 67,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 23,54</t>
+          <t>-2,26; 24,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 18,14</t>
+          <t>-9,27; 17,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,98; 73,34</t>
+          <t>55,36; 73,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 22,11</t>
+          <t>1,08; 22,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 12,13</t>
+          <t>-7,79; 11,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54,44; 68,08</t>
+          <t>54,2; 67,82</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 79,71</t>
+          <t>-8,56; 85,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 46,44</t>
+          <t>-31,17; 47,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>99,57; 240,68</t>
+          <t>95,1; 226,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 85,14</t>
+          <t>-6,6; 84,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 66,2</t>
+          <t>-23,07; 63,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>126,94; 286,43</t>
+          <t>128,63; 286,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 70,9</t>
+          <t>2,54; 73,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 38,42</t>
+          <t>-19,18; 37,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>129,25; 228,93</t>
+          <t>126,68; 228,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 15,63</t>
+          <t>-14,91; 16,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 26,49</t>
+          <t>-4,23; 27,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,04; 58,26</t>
+          <t>36,34; 58,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 12,75</t>
+          <t>-16,74; 13,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 13,15</t>
+          <t>-15,65; 15,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,18; 53,35</t>
+          <t>30,4; 52,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 9,88</t>
+          <t>-11,25; 10,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 15,68</t>
+          <t>-6,82; 16,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>36,48; 51,97</t>
+          <t>36,58; 52,47</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 36,74</t>
+          <t>-27,78; 41,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 65,22</t>
+          <t>-8,53; 64,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64,88; 148,99</t>
+          <t>63,52; 151,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 27,55</t>
+          <t>-30,03; 30,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,44; 28,93</t>
+          <t>-27,3; 33,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,78; 124,46</t>
+          <t>52,18; 123,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 21,69</t>
+          <t>-21,14; 24,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 34,68</t>
+          <t>-12,75; 36,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>64,95; 117,6</t>
+          <t>66,13; 123,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 20,24</t>
+          <t>-42,94; 19,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-45,06; 14,33</t>
+          <t>-46,71; 8,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,97; 63,33</t>
+          <t>12,97; 62,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 44,35</t>
+          <t>-12,44; 43,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 32,72</t>
+          <t>-22,31; 34,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,05; 83,32</t>
+          <t>33,78; 83,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 27,35</t>
+          <t>-16,55; 29,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-24,96; 15,78</t>
+          <t>-25,76; 15,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,56; 68,89</t>
+          <t>30,46; 66,19</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,13; 43,39</t>
+          <t>-52,45; 51,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,83; 37,61</t>
+          <t>-56,45; 21,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14,9; 172,69</t>
+          <t>14,9; 165,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 321,45</t>
+          <t>-24,9; 296,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 245,62</t>
+          <t>-40,65; 264,38</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,54; 669,83</t>
+          <t>54,66; 668,28</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 81,73</t>
+          <t>-27,7; 93,13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 52,2</t>
+          <t>-41,18; 46,59</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>44,31; 228,03</t>
+          <t>48,89; 220,87</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 33,09</t>
+          <t>-0,41; 32,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 25,22</t>
+          <t>-14,89; 22,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42,42; 68,1</t>
+          <t>42,23; 68,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,42; 31,23</t>
+          <t>-1,25; 31,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 5,37</t>
+          <t>-27,11; 9,67</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,39; 63,44</t>
+          <t>41,49; 64,34</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,13; 29,03</t>
+          <t>5,31; 27,95</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 10,11</t>
+          <t>-16,24; 8,65</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>45,41; 62,81</t>
+          <t>44,84; 62,74</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 123,89</t>
+          <t>-1,94; 112,4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 92,55</t>
+          <t>-35,46; 76,42</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>89,73; 266,2</t>
+          <t>86,87; 258,82</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1,45; 93,08</t>
+          <t>-2,22; 94,36</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,69; 14,11</t>
+          <t>-58,27; 27,15</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>78,25; 207,17</t>
+          <t>78,46; 204,28</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,8; 84,45</t>
+          <t>11,89; 85,57</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 28,83</t>
+          <t>-36,91; 24,79</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>96,94; 196,33</t>
+          <t>95,35; 198,53</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,96; 28,29</t>
+          <t>6,95; 29,13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 4,9</t>
+          <t>-15,45; 4,78</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51,35; 66,82</t>
+          <t>50,31; 65,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,8; 23,88</t>
+          <t>1,63; 23,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 2,38</t>
+          <t>-18,3; 3,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45,88; 62,17</t>
+          <t>45,17; 61,3</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,25; 22,45</t>
+          <t>8,03; 23,63</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 1,66</t>
+          <t>-13,61; 0,88</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>50,69; 62,3</t>
+          <t>50,53; 61,81</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>15,6; 91,62</t>
+          <t>15,93; 93,62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-40,0; 16,03</t>
+          <t>-36,64; 15,7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>117,62; 225,67</t>
+          <t>116,73; 226,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,25; 68,3</t>
+          <t>3,51; 65,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,15; 6,72</t>
+          <t>-38,02; 9,15</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>93,64; 182,77</t>
+          <t>91,28; 177,63</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,01; 65,65</t>
+          <t>18,32; 66,94</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 4,71</t>
+          <t>-32,14; 2,38</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>115,91; 185,79</t>
+          <t>113,69; 184,71</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 0,24</t>
+          <t>-22,34; -0,54</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 7,36</t>
+          <t>-13,98; 7,01</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>36,75; 55,97</t>
+          <t>35,93; 56,18</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 2,85</t>
+          <t>-18,46; 1,84</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 3,29</t>
+          <t>-17,57; 3,76</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>36,34; 54,33</t>
+          <t>35,55; 54,2</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-16,32; -1,06</t>
+          <t>-16,59; -1,52</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 2,56</t>
+          <t>-12,67; 1,85</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>39,92; 52,75</t>
+          <t>39,91; 52,68</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-45,86; 0,67</t>
+          <t>-46,15; -1,37</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 22,18</t>
+          <t>-29,31; 20,8</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>76,72; 167,84</t>
+          <t>71,46; 164,63</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 6,79</t>
+          <t>-35,5; 4,52</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 8,71</t>
+          <t>-33,76; 8,94</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>66,86; 139,34</t>
+          <t>66,76; 139,68</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-34,26; -3,02</t>
+          <t>-34,28; -3,96</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 6,4</t>
+          <t>-26,23; 4,64</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>79,7; 137,92</t>
+          <t>80,04; 135,75</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,01</t>
+          <t>1,3; 11,69</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 7,43</t>
+          <t>-2,2; 7,93</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>51,31; 59,17</t>
+          <t>51,67; 59,09</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,78; 10,25</t>
+          <t>-0,08; 9,98</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 3,11</t>
+          <t>-6,51; 3,05</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,92; 55,59</t>
+          <t>48,12; 55,69</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,46; 9,48</t>
+          <t>2,43; 9,85</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 3,7</t>
+          <t>-3,34; 3,85</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>51,08; 55,96</t>
+          <t>50,57; 56,07</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>5,2; 32,59</t>
+          <t>3,02; 31,24</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 19,49</t>
+          <t>-5,32; 21,54</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>118,3; 163,26</t>
+          <t>119,88; 162,57</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1,67; 25,45</t>
+          <t>-0,18; 24,89</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 7,59</t>
+          <t>-14,91; 7,42</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>103,22; 139,85</t>
+          <t>104,49; 141,65</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,71; 23,8</t>
+          <t>5,42; 24,75</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 9,45</t>
+          <t>-7,67; 9,79</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>116,95; 142,41</t>
+          <t>115,41; 144,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,58; 47,31</t>
+          <t>11,96; 46,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 32,94</t>
+          <t>1,63; 33,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,31; 75,43</t>
+          <t>53,44; 74,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 37,69</t>
+          <t>4,46; 38,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 37,75</t>
+          <t>8,11; 37,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,89; 76,61</t>
+          <t>54,3; 75,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,79; 37,78</t>
+          <t>11,9; 37,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,65; 32,19</t>
+          <t>8,55; 31,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,94; 73,03</t>
+          <t>57,48; 72,67</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,49; 189,51</t>
+          <t>27,81; 182,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 130,65</t>
+          <t>4,85; 132,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116,82; 319,91</t>
+          <t>121,07; 311,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 151,95</t>
+          <t>10,87; 155,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,37; 148,24</t>
+          <t>19,52; 157,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>123,2; 330,37</t>
+          <t>120,14; 318,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,33; 138,29</t>
+          <t>31,26; 132,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,69; 112,77</t>
+          <t>21,01; 112,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>141,15; 283,27</t>
+          <t>137,99; 271,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 18,69</t>
+          <t>-11,24; 17,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 27,58</t>
+          <t>-0,65; 26,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,6; 69,12</t>
+          <t>48,14; 68,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 9,57</t>
+          <t>-19,12; 9,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 10,13</t>
+          <t>-16,29; 9,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,71; 55,4</t>
+          <t>33,37; 55,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 10,35</t>
+          <t>-10,22; 10,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 15,33</t>
+          <t>-3,01; 15,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,8; 59,35</t>
+          <t>43,93; 59,5</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 55,38</t>
+          <t>-25,28; 51,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 84,34</t>
+          <t>-0,39; 84,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96,31; 224,88</t>
+          <t>93,76; 217,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,58; 24,17</t>
+          <t>-34,39; 22,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 24,33</t>
+          <t>-29,24; 23,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,92; 141,86</t>
+          <t>56,41; 142,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 25,08</t>
+          <t>-21,32; 28,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 39,14</t>
+          <t>-6,23; 38,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88,95; 159,74</t>
+          <t>86,42; 162,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 26,3</t>
+          <t>-4,5; 26,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 14,74</t>
+          <t>-14,6; 15,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,21; 67,07</t>
+          <t>45,94; 67,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 24,24</t>
+          <t>-1,75; 24,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 17,74</t>
+          <t>-8,58; 16,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,36; 73,29</t>
+          <t>55,79; 73,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 22,89</t>
+          <t>0,03; 20,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 11,85</t>
+          <t>-7,04; 12,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54,2; 67,82</t>
+          <t>54,7; 68,57</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 85,72</t>
+          <t>-9,48; 86,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 47,91</t>
+          <t>-32,41; 51,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95,1; 226,52</t>
+          <t>94,17; 236,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 84,08</t>
+          <t>-4,37; 87,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 63,16</t>
+          <t>-21,93; 59,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>128,63; 286,36</t>
+          <t>129,95; 278,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,54; 73,97</t>
+          <t>-0,31; 64,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 37,0</t>
+          <t>-17,67; 39,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>126,68; 228,44</t>
+          <t>129,4; 233,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 16,65</t>
+          <t>-14,32; 16,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 27,17</t>
+          <t>-4,03; 26,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,34; 58,5</t>
+          <t>37,06; 58,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 13,65</t>
+          <t>-18,95; 12,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 15,52</t>
+          <t>-17,61; 16,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,4; 52,49</t>
+          <t>29,88; 52,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 10,55</t>
+          <t>-11,72; 10,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 16,01</t>
+          <t>-5,97; 15,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>36,58; 52,47</t>
+          <t>35,92; 52,17</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 41,08</t>
+          <t>-26,34; 42,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 64,86</t>
+          <t>-6,7; 66,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63,52; 151,92</t>
+          <t>65,69; 156,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 30,91</t>
+          <t>-32,49; 29,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 33,43</t>
+          <t>-30,38; 34,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,18; 123,41</t>
+          <t>51,18; 122,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 24,0</t>
+          <t>-20,69; 24,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 36,6</t>
+          <t>-11,51; 34,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>66,13; 123,84</t>
+          <t>65,42; 119,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 19,86</t>
+          <t>-41,47; 22,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 8,94</t>
+          <t>-45,0; 9,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,97; 62,39</t>
+          <t>13,22; 63,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 43,59</t>
+          <t>-11,7; 47,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 34,09</t>
+          <t>-21,89; 32,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,78; 83,68</t>
+          <t>32,87; 83,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 29,74</t>
+          <t>-20,5; 25,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 15,13</t>
+          <t>-26,08; 14,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,46; 66,19</t>
+          <t>30,03; 65,91</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-52,45; 51,93</t>
+          <t>-51,59; 49,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,45; 21,42</t>
+          <t>-53,74; 19,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14,9; 165,9</t>
+          <t>15,23; 175,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,9; 296,83</t>
+          <t>-25,14; 352,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,65; 264,38</t>
+          <t>-40,67; 253,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,66; 668,28</t>
+          <t>51,7; 668,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 93,13</t>
+          <t>-31,6; 80,74</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 46,59</t>
+          <t>-39,88; 46,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>48,89; 220,87</t>
+          <t>46,49; 210,82</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 32,11</t>
+          <t>-2,32; 33,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 22,27</t>
+          <t>-13,83; 25,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42,23; 68,0</t>
+          <t>42,12; 69,45</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 31,55</t>
+          <t>0,39; 31,77</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 9,67</t>
+          <t>-28,36; 7,73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,49; 64,34</t>
+          <t>40,32; 63,09</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,31; 27,95</t>
+          <t>4,24; 27,7</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 8,65</t>
+          <t>-16,32; 9,09</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>44,84; 62,74</t>
+          <t>45,3; 62,48</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 112,4</t>
+          <t>-4,25; 127,28</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 76,42</t>
+          <t>-33,11; 93,14</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>86,87; 258,82</t>
+          <t>86,41; 279,83</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 94,36</t>
+          <t>1,06; 92,78</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-58,27; 27,15</t>
+          <t>-59,47; 20,82</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>78,46; 204,28</t>
+          <t>76,1; 193,33</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,89; 85,57</t>
+          <t>9,61; 82,85</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 24,79</t>
+          <t>-37,09; 25,72</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>95,35; 198,53</t>
+          <t>97,96; 194,88</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,95; 29,13</t>
+          <t>6,51; 27,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 4,78</t>
+          <t>-14,68; 5,06</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50,31; 65,9</t>
+          <t>51,16; 66,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,63; 23,44</t>
+          <t>1,29; 22,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 3,44</t>
+          <t>-16,78; 3,35</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45,17; 61,3</t>
+          <t>45,65; 61,51</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,03; 23,63</t>
+          <t>7,23; 22,67</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 0,88</t>
+          <t>-13,26; 1,17</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>50,53; 61,81</t>
+          <t>50,35; 62,22</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>15,93; 93,62</t>
+          <t>13,82; 86,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-36,64; 15,7</t>
+          <t>-36,62; 16,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>116,73; 226,79</t>
+          <t>117,95; 226,75</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3,51; 65,18</t>
+          <t>2,21; 61,71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-38,02; 9,15</t>
+          <t>-37,05; 9,17</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>91,28; 177,63</t>
+          <t>93,14; 173,06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,32; 66,94</t>
+          <t>16,5; 65,38</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 2,38</t>
+          <t>-31,38; 3,52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>113,69; 184,71</t>
+          <t>113,1; 185,06</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-22,34; -0,54</t>
+          <t>-20,85; 0,04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 7,01</t>
+          <t>-14,29; 7,89</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>35,93; 56,18</t>
+          <t>36,43; 55,69</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 1,84</t>
+          <t>-18,58; 2,1</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 3,76</t>
+          <t>-18,08; 3,48</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>35,55; 54,2</t>
+          <t>36,26; 54,54</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-16,59; -1,52</t>
+          <t>-16,35; -1,64</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 1,85</t>
+          <t>-13,27; 1,53</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>39,91; 52,68</t>
+          <t>39,23; 52,23</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-46,15; -1,37</t>
+          <t>-43,51; -0,42</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,31; 20,8</t>
+          <t>-28,74; 23,75</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>71,46; 164,63</t>
+          <t>75,95; 165,47</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 4,52</t>
+          <t>-36,07; 4,98</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 8,94</t>
+          <t>-33,93; 9,53</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>66,76; 139,68</t>
+          <t>66,65; 139,92</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-34,28; -3,96</t>
+          <t>-33,66; -3,28</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 4,64</t>
+          <t>-27,02; 3,92</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>80,04; 135,75</t>
+          <t>79,22; 133,62</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,3; 11,69</t>
+          <t>1,66; 11,84</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 7,93</t>
+          <t>-1,93; 7,82</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>51,67; 59,09</t>
+          <t>51,66; 59,35</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 9,98</t>
+          <t>0,74; 10,59</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 3,05</t>
+          <t>-6,86; 3,39</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>48,12; 55,69</t>
+          <t>48,09; 55,62</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,43; 9,85</t>
+          <t>2,51; 9,75</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,85</t>
+          <t>-3,24; 3,72</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>50,57; 56,07</t>
+          <t>51,03; 56,55</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>3,02; 31,24</t>
+          <t>4,02; 31,91</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 21,54</t>
+          <t>-4,77; 21,29</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>119,88; 162,57</t>
+          <t>119,96; 163,23</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 24,89</t>
+          <t>1,49; 26,05</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 7,42</t>
+          <t>-15,01; 8,38</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>104,49; 141,65</t>
+          <t>103,95; 140,02</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,42; 24,75</t>
+          <t>5,73; 24,53</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 9,79</t>
+          <t>-7,53; 9,24</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>115,41; 144,12</t>
+          <t>117,79; 146,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20,73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22,69</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>66,16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>30,67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>18,5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>65,57</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>65,37</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,68</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>20,73</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,69</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>66,21</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,68</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20,73</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>65,9</t>
+          <t>65,78</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,96; 46,72</t>
+          <t>3,78; 37,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 33,7</t>
+          <t>6,86; 39,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,44; 74,66</t>
+          <t>54,97; 76,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 38,35</t>
+          <t>11,19; 46,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,11; 37,72</t>
+          <t>1,93; 34,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,3; 75,45</t>
+          <t>54,89; 75,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,9; 37,02</t>
+          <t>11,11; 37,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 31,65</t>
+          <t>8,96; 32,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,48; 72,67</t>
+          <t>57,46; 73,29</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>62,47%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68,38%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>199,36%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>91,69%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>55,32%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>196,05%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>62,47%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>68,38%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>199,52%</t>
+          <t>195,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>197,84%</t>
+          <t>197,49%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,81; 182,96</t>
+          <t>10,81; 155,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 132,31</t>
+          <t>15,6; 154,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121,07; 311,34</t>
+          <t>124,13; 338,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,87; 155,56</t>
+          <t>27,47; 173,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,52; 157,46</t>
+          <t>3,79; 129,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>120,14; 318,65</t>
+          <t>126,27; 322,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,26; 132,84</t>
+          <t>29,87; 138,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,01; 112,36</t>
+          <t>22,43; 119,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>137,99; 271,54</t>
+          <t>139,66; 283,62</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,79</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45,21</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>14,29</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58,65</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,99</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,79</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,88</t>
+          <t>58,41</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>51,85</t>
+          <t>51,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 17,87</t>
+          <t>-19,0; 9,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 26,97</t>
+          <t>-16,66; 9,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,14; 68,32</t>
+          <t>34,63; 55,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 9,74</t>
+          <t>-13,57; 16,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 9,74</t>
+          <t>-2,62; 26,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,37; 55,55</t>
+          <t>48,44; 67,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 10,91</t>
+          <t>-11,36; 9,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 15,07</t>
+          <t>-4,55; 15,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,93; 59,5</t>
+          <t>43,94; 58,71</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-8,23%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-5,76%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>93,29%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>8,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>35,39%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>145,24%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-8,23%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-5,76%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>144,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>116,96%</t>
+          <t>116,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 51,67</t>
+          <t>-34,41; 24,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 84,6</t>
+          <t>-30,86; 22,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93,76; 217,56</t>
+          <t>59,78; 140,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 22,8</t>
+          <t>-26,72; 47,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 23,1</t>
+          <t>-4,76; 79,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,41; 142,17</t>
+          <t>96,93; 215,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 28,0</t>
+          <t>-23,34; 25,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 38,37</t>
+          <t>-9,06; 39,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,42; 162,06</t>
+          <t>86,66; 156,86</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,01</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,07</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>64,9</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>11,34</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,16</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>57,41</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,01</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,07</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,94</t>
+          <t>57,32</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61,35</t>
+          <t>61,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 26,59</t>
+          <t>-3,29; 23,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 15,53</t>
+          <t>-8,73; 18,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,94; 67,06</t>
+          <t>54,96; 73,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 24,87</t>
+          <t>-5,15; 25,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 16,7</t>
+          <t>-14,87; 14,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,79; 73,21</t>
+          <t>46,25; 67,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 20,67</t>
+          <t>0,71; 22,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 12,07</t>
+          <t>-7,19; 12,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54,7; 68,57</t>
+          <t>54,22; 67,88</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>32,33%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>190,61%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>29,72%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>150,44%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>32,33%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>190,72%</t>
+          <t>150,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>170,14%</t>
+          <t>169,75%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 86,39</t>
+          <t>-7,73; 85,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,41; 51,03</t>
+          <t>-22,02; 66,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94,17; 236,14</t>
+          <t>126,89; 286,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 87,55</t>
+          <t>-11,51; 79,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 59,18</t>
+          <t>-34,34; 46,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>129,95; 278,78</t>
+          <t>99,45; 240,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 64,11</t>
+          <t>1,55; 70,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 39,21</t>
+          <t>-17,88; 38,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>129,4; 233,14</t>
+          <t>129,0; 229,04</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,07</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42,38</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>11,2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>47,84</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,07</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,14</t>
+          <t>48,33</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>44,84</t>
+          <t>45,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 16,97</t>
+          <t>-17,95; 12,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 26,4</t>
+          <t>-16,5; 13,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,06; 58,9</t>
+          <t>30,4; 53,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 12,98</t>
+          <t>-14,94; 15,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 16,08</t>
+          <t>-6,23; 26,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,88; 52,13</t>
+          <t>37,36; 58,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 10,98</t>
+          <t>-11,88; 9,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 15,8</t>
+          <t>-6,2; 15,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>35,92; 52,17</t>
+          <t>36,99; 52,08</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-3,98%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-1,72%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>81,45%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>2,38%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>23,7%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>101,21%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-3,98%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-1,72%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>102,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 42,79</t>
+          <t>-31,43; 27,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 66,01</t>
+          <t>-29,44; 28,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65,69; 156,44</t>
+          <t>51,33; 124,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,49; 29,29</t>
+          <t>-28,65; 36,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,38; 34,32</t>
+          <t>-11,28; 65,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,18; 122,88</t>
+          <t>65,94; 149,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 24,64</t>
+          <t>-22,49; 21,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 34,09</t>
+          <t>-11,32; 34,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>65,42; 119,5</t>
+          <t>65,73; 118,56</t>
         </is>
       </c>
     </row>
@@ -1488,34 +1488,34 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>18,24</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7,36</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>64,01</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-11,02</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-18,85</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>34,48</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18,24</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,36</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>61,74</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>4,79</t>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>49,34</t>
+          <t>50,61</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-41,47; 22,72</t>
+          <t>-13,12; 44,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 9,89</t>
+          <t>-17,96; 32,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,22; 63,68</t>
+          <t>37,69; 84,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 47,64</t>
+          <t>-40,92; 20,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 32,53</t>
+          <t>-45,06; 14,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,87; 83,34</t>
+          <t>12,97; 63,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 25,61</t>
+          <t>-16,24; 27,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-26,08; 14,73</t>
+          <t>-24,96; 15,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,03; 65,91</t>
+          <t>31,63; 68,97</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1594,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>55,79%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>22,52%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>195,75%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-16,82%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-28,77%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>52,62%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>55,79%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>22,52%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>188,81%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>10,06%</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>103,53%</t>
+          <t>106,21%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,59; 49,82</t>
+          <t>-24,79; 321,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 19,61</t>
+          <t>-35,38; 245,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15,23; 175,3</t>
+          <t>64,42; 678,54</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 352,31</t>
+          <t>-51,13; 43,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 253,49</t>
+          <t>-53,83; 37,61</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,7; 668,32</t>
+          <t>14,9; 172,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 80,74</t>
+          <t>-27,02; 81,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-39,88; 46,66</t>
+          <t>-38,86; 52,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>46,49; 210,82</t>
+          <t>47,06; 227,48</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>16,48</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-10,87</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>52,0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>16,45</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>4,03</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>55,84</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>16,48</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-10,87</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>52,36</t>
+          <t>56,82</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>54,06</t>
+          <t>54,26</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 33,6</t>
+          <t>0,42; 31,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 25,82</t>
+          <t>-28,73; 5,37</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42,12; 69,45</t>
+          <t>40,0; 63,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,39; 31,77</t>
+          <t>-1,44; 33,09</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 7,73</t>
+          <t>-13,58; 25,22</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,32; 63,09</t>
+          <t>43,18; 68,62</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,24; 27,7</t>
+          <t>5,13; 29,03</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 9,09</t>
+          <t>-17,04; 10,11</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>45,3; 62,48</t>
+          <t>46,16; 63,04</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>38,78%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-25,57%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>122,33%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>45,45%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>11,12%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>154,24%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>38,78%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-25,57%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>123,17%</t>
+          <t>156,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>136,74%</t>
+          <t>137,23%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 127,28</t>
+          <t>1,45; 93,08</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 93,14</t>
+          <t>-60,69; 14,11</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>86,41; 279,83</t>
+          <t>77,33; 204,47</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1,06; 92,78</t>
+          <t>-3,64; 123,89</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-59,47; 20,82</t>
+          <t>-33,59; 92,55</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>76,1; 193,33</t>
+          <t>92,32; 271,97</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,61; 82,85</t>
+          <t>11,8; 84,45</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 25,72</t>
+          <t>-38,36; 28,83</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>97,96; 194,88</t>
+          <t>97,43; 196,82</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>12,65</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-7,31</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>53,55</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>17,69</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-5,18</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>59,13</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>12,65</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-7,31</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,94</t>
+          <t>58,86</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>56,55</t>
+          <t>56,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,51; 27,3</t>
+          <t>1,8; 23,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 5,06</t>
+          <t>-18,54; 2,38</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51,16; 66,39</t>
+          <t>45,4; 61,6</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,29; 22,35</t>
+          <t>6,96; 28,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 3,35</t>
+          <t>-16,55; 4,9</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45,65; 61,51</t>
+          <t>50,82; 66,52</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,23; 22,67</t>
+          <t>7,25; 22,45</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 1,17</t>
+          <t>-13,26; 1,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>50,35; 62,22</t>
+          <t>50,3; 61,95</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>30,46%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-17,61%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>128,97%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>48,96%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-14,33%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>163,66%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>30,46%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-17,61%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>129,92%</t>
+          <t>162,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>145,64%</t>
+          <t>144,75%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>13,82; 86,89</t>
+          <t>4,25; 68,3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 16,81</t>
+          <t>-39,15; 6,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>117,95; 226,75</t>
+          <t>92,71; 181,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,21; 61,71</t>
+          <t>15,6; 91,62</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-37,05; 9,17</t>
+          <t>-40,0; 16,03</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>93,14; 173,06</t>
+          <t>116,61; 223,66</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,5; 65,38</t>
+          <t>18,01; 65,65</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 3,52</t>
+          <t>-31,42; 4,71</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>113,1; 185,06</t>
+          <t>115,08; 184,51</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-7,79</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-6,87</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>45,64</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-10,58</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-3,63</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>46,79</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-7,79</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-6,87</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,43</t>
+          <t>47,25</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>46,16</t>
+          <t>46,45</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 0,04</t>
+          <t>-17,8; 2,85</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 7,89</t>
+          <t>-17,58; 3,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>36,43; 55,69</t>
+          <t>36,83; 54,54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 2,1</t>
+          <t>-21,54; 0,24</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 3,48</t>
+          <t>-14,55; 7,36</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>36,26; 54,54</t>
+          <t>37,39; 56,47</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-16,35; -1,64</t>
+          <t>-16,32; -1,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 1,53</t>
+          <t>-12,62; 2,56</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>39,23; 52,23</t>
+          <t>40,1; 53,13</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-16,93%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-14,92%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-25,29%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-8,67%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>111,77%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-16,93%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-14,92%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>112,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>104,86%</t>
+          <t>105,52%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-43,51; -0,42</t>
+          <t>-35,27; 6,79</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 23,75</t>
+          <t>-33,42; 8,71</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>75,95; 165,47</t>
+          <t>68,61; 141,2</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-36,07; 4,98</t>
+          <t>-45,86; 0,67</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 9,53</t>
+          <t>-29,72; 22,18</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>66,65; 139,92</t>
+          <t>77,24; 168,25</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-33,66; -3,28</t>
+          <t>-34,26; -3,02</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 3,92</t>
+          <t>-26,97; 6,4</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>79,22; 133,62</t>
+          <t>80,31; 138,59</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>5,28</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-1,72</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>51,97</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>6,86</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>2,62</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>55,36</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>5,28</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-1,72</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>51,97</t>
+          <t>55,12</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>53,62</t>
+          <t>53,51</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,66; 11,84</t>
+          <t>0,78; 10,25</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 7,82</t>
+          <t>-6,55; 3,11</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>51,66; 59,35</t>
+          <t>48,03; 55,71</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,74; 10,59</t>
+          <t>2,14; 12,01</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,39</t>
+          <t>-2,49; 7,43</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>48,09; 55,62</t>
+          <t>50,96; 58,89</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,75</t>
+          <t>2,46; 9,48</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,72</t>
+          <t>-3,25; 3,7</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>51,03; 56,55</t>
+          <t>50,87; 55,9</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-4,01%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>121,42%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>17,27%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>6,59%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>139,23%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-4,01%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>121,43%</t>
+          <t>138,64%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>129,77%</t>
+          <t>129,5%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>4,02; 31,91</t>
+          <t>1,67; 25,45</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 21,29</t>
+          <t>-14,48; 7,59</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>119,96; 163,23</t>
+          <t>103,51; 140,34</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1,49; 26,05</t>
+          <t>5,2; 32,59</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 8,38</t>
+          <t>-5,99; 19,49</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>103,95; 140,02</t>
+          <t>117,52; 162,48</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,73; 24,53</t>
+          <t>5,71; 23,8</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 9,24</t>
+          <t>-7,52; 9,45</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>117,79; 146,31</t>
+          <t>116,91; 142,37</t>
         </is>
       </c>
     </row>
